--- a/data_fix.xlsx
+++ b/data_fix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gusca\OneDrive\Documentos\research\photomonitoring_fran\photomonitoring-chile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401B1406-4FB4-41A6-A887-601FA03A2C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2808B3D-EC7D-4EE5-95D8-04A7C5956AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="-11520" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1980" yWindow="-11640" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="666">
   <si>
     <t>classification</t>
   </si>
@@ -1525,9 +1525,6 @@
     <t>Gallinago magellanica</t>
   </si>
   <si>
-    <t>Bovinae</t>
-  </si>
-  <si>
     <t>subfamily</t>
   </si>
   <si>
@@ -1741,9 +1738,6 @@
     <t>Lama guanicoe</t>
   </si>
   <si>
-    <t>Rattus norvegicus</t>
-  </si>
-  <si>
     <t>Leopardus guigna</t>
   </si>
   <si>
@@ -1807,9 +1801,6 @@
     <t>Lama glama × Lama guanicoe</t>
   </si>
   <si>
-    <t>hybrid</t>
-  </si>
-  <si>
     <t>Leistes loyca</t>
   </si>
   <si>
@@ -1825,9 +1816,6 @@
     <t>Mammalia</t>
   </si>
   <si>
-    <t>Geositta cunicularia</t>
-  </si>
-  <si>
     <t>Geositta punensis</t>
   </si>
   <si>
@@ -2006,6 +1994,30 @@
   </si>
   <si>
     <t>Turdus falcklandii</t>
+  </si>
+  <si>
+    <t>Chloephaga</t>
+  </si>
+  <si>
+    <t>Pygarrhichas</t>
+  </si>
+  <si>
+    <t>cwf, ERROR ES UN YAL</t>
+  </si>
+  <si>
+    <t>Rattus</t>
+  </si>
+  <si>
+    <t>hybrid, ERROR llama Y guanacos</t>
+  </si>
+  <si>
+    <t>Geositta</t>
+  </si>
+  <si>
+    <t>divide later</t>
+  </si>
+  <si>
+    <t>Thylamys</t>
   </si>
 </sst>
 </file>
@@ -2383,9 +2395,6 @@
       <c r="C3" t="s">
         <v>483</v>
       </c>
-      <c r="D3" t="s">
-        <v>485</v>
-      </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
@@ -2409,13 +2418,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>487</v>
+        <v>566</v>
       </c>
       <c r="C5" t="s">
-        <v>487</v>
-      </c>
-      <c r="D5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -2445,9 +2451,6 @@
       <c r="C7" t="s">
         <v>483</v>
       </c>
-      <c r="D7" t="s">
-        <v>485</v>
-      </c>
       <c r="E7" t="s">
         <v>17</v>
       </c>
@@ -2476,9 +2479,6 @@
       <c r="C9" t="s">
         <v>492</v>
       </c>
-      <c r="D9" t="s">
-        <v>485</v>
-      </c>
       <c r="E9" t="s">
         <v>21</v>
       </c>
@@ -2660,9 +2660,6 @@
       <c r="C20" t="s">
         <v>483</v>
       </c>
-      <c r="D20" t="s">
-        <v>485</v>
-      </c>
       <c r="E20" t="s">
         <v>39</v>
       </c>
@@ -2740,13 +2737,10 @@
         <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>501</v>
+        <v>647</v>
       </c>
       <c r="C25" t="s">
-        <v>502</v>
-      </c>
-      <c r="D25" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
@@ -2757,13 +2751,10 @@
         <v>47</v>
       </c>
       <c r="B26" t="s">
+        <v>502</v>
+      </c>
+      <c r="C26" t="s">
         <v>503</v>
-      </c>
-      <c r="C26" t="s">
-        <v>504</v>
-      </c>
-      <c r="D26" t="s">
-        <v>485</v>
       </c>
       <c r="E26" t="s">
         <v>48</v>
@@ -2774,7 +2765,7 @@
         <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C27" t="s">
         <v>483</v>
@@ -2791,7 +2782,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C28" t="s">
         <v>483</v>
@@ -2808,7 +2799,7 @@
         <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C29" t="s">
         <v>483</v>
@@ -2825,7 +2816,7 @@
         <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C30" t="s">
         <v>483</v>
@@ -2842,7 +2833,7 @@
         <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C31" t="s">
         <v>483</v>
@@ -2859,7 +2850,7 @@
         <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C32" t="s">
         <v>483</v>
@@ -2876,7 +2867,7 @@
         <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C33" t="s">
         <v>483</v>
@@ -2893,7 +2884,7 @@
         <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C34" t="s">
         <v>483</v>
@@ -2944,7 +2935,7 @@
         <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C37" t="s">
         <v>483</v>
@@ -2961,13 +2952,10 @@
         <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>512</v>
+        <v>658</v>
       </c>
       <c r="C38" t="s">
-        <v>483</v>
-      </c>
-      <c r="D38" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E38" t="s">
         <v>69</v>
@@ -2978,13 +2966,10 @@
         <v>70</v>
       </c>
       <c r="B39" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C39" t="s">
         <v>483</v>
-      </c>
-      <c r="D39" t="s">
-        <v>485</v>
       </c>
       <c r="E39" t="s">
         <v>21</v>
@@ -2995,7 +2980,7 @@
         <v>71</v>
       </c>
       <c r="B40" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C40" t="s">
         <v>483</v>
@@ -3012,7 +2997,7 @@
         <v>73</v>
       </c>
       <c r="B41" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C41" t="s">
         <v>483</v>
@@ -3029,7 +3014,7 @@
         <v>74</v>
       </c>
       <c r="B42" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C42" t="s">
         <v>483</v>
@@ -3046,13 +3031,10 @@
         <v>76</v>
       </c>
       <c r="B43" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C43" t="s">
         <v>483</v>
-      </c>
-      <c r="D43" t="s">
-        <v>485</v>
       </c>
       <c r="E43" t="s">
         <v>77</v>
@@ -3063,7 +3045,7 @@
         <v>78</v>
       </c>
       <c r="B44" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C44" t="s">
         <v>483</v>
@@ -3097,7 +3079,7 @@
         <v>80</v>
       </c>
       <c r="B46" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C46" t="s">
         <v>483</v>
@@ -3114,7 +3096,7 @@
         <v>82</v>
       </c>
       <c r="B47" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C47" t="s">
         <v>483</v>
@@ -3131,7 +3113,7 @@
         <v>84</v>
       </c>
       <c r="B48" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C48" t="s">
         <v>483</v>
@@ -3148,7 +3130,7 @@
         <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C49" t="s">
         <v>483</v>
@@ -3165,7 +3147,7 @@
         <v>88</v>
       </c>
       <c r="B50" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C50" t="s">
         <v>483</v>
@@ -3182,13 +3164,10 @@
         <v>89</v>
       </c>
       <c r="B51" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C51" t="s">
         <v>483</v>
-      </c>
-      <c r="D51" t="s">
-        <v>485</v>
       </c>
       <c r="E51" t="s">
         <v>21</v>
@@ -3199,7 +3178,7 @@
         <v>90</v>
       </c>
       <c r="B52" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C52" t="s">
         <v>483</v>
@@ -3216,7 +3195,7 @@
         <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C53" t="s">
         <v>483</v>
@@ -3233,13 +3212,10 @@
         <v>93</v>
       </c>
       <c r="B54" t="s">
+        <v>520</v>
+      </c>
+      <c r="C54" t="s">
         <v>521</v>
-      </c>
-      <c r="C54" t="s">
-        <v>522</v>
-      </c>
-      <c r="D54" t="s">
-        <v>485</v>
       </c>
       <c r="E54" t="s">
         <v>94</v>
@@ -3250,7 +3226,7 @@
         <v>95</v>
       </c>
       <c r="B55" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C55" t="s">
         <v>483</v>
@@ -3264,13 +3240,10 @@
         <v>97</v>
       </c>
       <c r="B56" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C56" t="s">
         <v>483</v>
-      </c>
-      <c r="D56" t="s">
-        <v>485</v>
       </c>
       <c r="E56" t="s">
         <v>98</v>
@@ -3281,7 +3254,7 @@
         <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C57" t="s">
         <v>483</v>
@@ -3298,7 +3271,7 @@
         <v>101</v>
       </c>
       <c r="B58" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C58" t="s">
         <v>483</v>
@@ -3315,7 +3288,7 @@
         <v>102</v>
       </c>
       <c r="B59" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C59" t="s">
         <v>483</v>
@@ -3332,7 +3305,7 @@
         <v>103</v>
       </c>
       <c r="B60" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C60" t="s">
         <v>483</v>
@@ -3349,7 +3322,7 @@
         <v>104</v>
       </c>
       <c r="B61" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C61" t="s">
         <v>483</v>
@@ -3366,7 +3339,7 @@
         <v>105</v>
       </c>
       <c r="B62" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C62" t="s">
         <v>483</v>
@@ -3383,7 +3356,7 @@
         <v>106</v>
       </c>
       <c r="B63" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C63" t="s">
         <v>483</v>
@@ -3400,7 +3373,7 @@
         <v>108</v>
       </c>
       <c r="B64" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C64" t="s">
         <v>483</v>
@@ -3417,7 +3390,7 @@
         <v>110</v>
       </c>
       <c r="B65" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C65" t="s">
         <v>483</v>
@@ -3434,7 +3407,7 @@
         <v>111</v>
       </c>
       <c r="B66" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C66" t="s">
         <v>483</v>
@@ -3451,13 +3424,10 @@
         <v>113</v>
       </c>
       <c r="B67" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C67" t="s">
         <v>483</v>
-      </c>
-      <c r="D67" t="s">
-        <v>485</v>
       </c>
       <c r="E67" t="s">
         <v>114</v>
@@ -3468,7 +3438,7 @@
         <v>115</v>
       </c>
       <c r="B68" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C68" t="s">
         <v>483</v>
@@ -3485,13 +3455,10 @@
         <v>116</v>
       </c>
       <c r="B69" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C69" t="s">
         <v>483</v>
-      </c>
-      <c r="D69" t="s">
-        <v>485</v>
       </c>
       <c r="E69" t="s">
         <v>21</v>
@@ -3502,13 +3469,10 @@
         <v>117</v>
       </c>
       <c r="B70" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C70" t="s">
         <v>483</v>
-      </c>
-      <c r="D70" t="s">
-        <v>485</v>
       </c>
       <c r="E70" t="s">
         <v>118</v>
@@ -3519,7 +3483,7 @@
         <v>119</v>
       </c>
       <c r="B71" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C71" t="s">
         <v>483</v>
@@ -3536,7 +3500,7 @@
         <v>121</v>
       </c>
       <c r="B72" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C72" t="s">
         <v>483</v>
@@ -3550,7 +3514,7 @@
         <v>123</v>
       </c>
       <c r="B73" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C73" t="s">
         <v>483</v>
@@ -3581,7 +3545,7 @@
         <v>126</v>
       </c>
       <c r="B75" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C75" t="s">
         <v>483</v>
@@ -3598,7 +3562,7 @@
         <v>127</v>
       </c>
       <c r="B76" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C76" t="s">
         <v>483</v>
@@ -3615,7 +3579,7 @@
         <v>128</v>
       </c>
       <c r="B77" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C77" t="s">
         <v>483</v>
@@ -3632,7 +3596,7 @@
         <v>129</v>
       </c>
       <c r="B78" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C78" t="s">
         <v>483</v>
@@ -3649,7 +3613,7 @@
         <v>130</v>
       </c>
       <c r="B79" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C79" t="s">
         <v>483</v>
@@ -3666,7 +3630,7 @@
         <v>132</v>
       </c>
       <c r="B80" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C80" t="s">
         <v>483</v>
@@ -3683,7 +3647,7 @@
         <v>134</v>
       </c>
       <c r="B81" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C81" t="s">
         <v>492</v>
@@ -3700,7 +3664,7 @@
         <v>135</v>
       </c>
       <c r="B82" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C82" t="s">
         <v>483</v>
@@ -3717,7 +3681,7 @@
         <v>136</v>
       </c>
       <c r="B83" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C83" t="s">
         <v>483</v>
@@ -3734,13 +3698,10 @@
         <v>138</v>
       </c>
       <c r="B84" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C84" t="s">
         <v>483</v>
-      </c>
-      <c r="D84" t="s">
-        <v>485</v>
       </c>
       <c r="E84" t="s">
         <v>85</v>
@@ -3751,13 +3712,10 @@
         <v>139</v>
       </c>
       <c r="B85" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C85" t="s">
         <v>483</v>
-      </c>
-      <c r="D85" t="s">
-        <v>485</v>
       </c>
       <c r="E85" t="s">
         <v>48</v>
@@ -3768,13 +3726,13 @@
         <v>140</v>
       </c>
       <c r="B86" t="s">
-        <v>543</v>
+        <v>659</v>
       </c>
       <c r="C86" t="s">
-        <v>483</v>
+        <v>521</v>
       </c>
       <c r="D86" t="s">
-        <v>485</v>
+        <v>660</v>
       </c>
       <c r="E86" t="s">
         <v>26</v>
@@ -3785,13 +3743,10 @@
         <v>141</v>
       </c>
       <c r="B87" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C87" t="s">
         <v>483</v>
-      </c>
-      <c r="D87" t="s">
-        <v>485</v>
       </c>
       <c r="E87" t="s">
         <v>19</v>
@@ -3802,13 +3757,10 @@
         <v>142</v>
       </c>
       <c r="B88" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C88" t="s">
-        <v>522</v>
-      </c>
-      <c r="D88" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E88" t="s">
         <v>143</v>
@@ -3819,7 +3771,7 @@
         <v>144</v>
       </c>
       <c r="B89" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C89" t="s">
         <v>483</v>
@@ -3836,13 +3788,10 @@
         <v>145</v>
       </c>
       <c r="B90" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C90" t="s">
         <v>483</v>
-      </c>
-      <c r="D90" t="s">
-        <v>485</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
@@ -3853,7 +3802,7 @@
         <v>146</v>
       </c>
       <c r="B91" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C91" t="s">
         <v>483</v>
@@ -3870,7 +3819,7 @@
         <v>147</v>
       </c>
       <c r="B92" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C92" t="s">
         <v>483</v>
@@ -3887,7 +3836,7 @@
         <v>149</v>
       </c>
       <c r="B93" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C93" t="s">
         <v>483</v>
@@ -3904,7 +3853,7 @@
         <v>150</v>
       </c>
       <c r="B94" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C94" t="s">
         <v>483</v>
@@ -3921,7 +3870,7 @@
         <v>151</v>
       </c>
       <c r="B95" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C95" t="s">
         <v>483</v>
@@ -3938,7 +3887,7 @@
         <v>153</v>
       </c>
       <c r="B96" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C96" t="s">
         <v>483</v>
@@ -3955,7 +3904,7 @@
         <v>155</v>
       </c>
       <c r="B97" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C97" t="s">
         <v>483</v>
@@ -3972,13 +3921,10 @@
         <v>157</v>
       </c>
       <c r="B98" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C98" t="s">
         <v>483</v>
-      </c>
-      <c r="D98" t="s">
-        <v>485</v>
       </c>
       <c r="E98" t="s">
         <v>24</v>
@@ -3989,13 +3935,10 @@
         <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C99" t="s">
         <v>492</v>
-      </c>
-      <c r="D99" t="s">
-        <v>485</v>
       </c>
       <c r="E99" t="s">
         <v>19</v>
@@ -4006,7 +3949,7 @@
         <v>159</v>
       </c>
       <c r="B100" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C100" t="s">
         <v>483</v>
@@ -4028,9 +3971,6 @@
       <c r="C101" t="s">
         <v>493</v>
       </c>
-      <c r="D101" t="s">
-        <v>485</v>
-      </c>
       <c r="E101" t="s">
         <v>21</v>
       </c>
@@ -4045,9 +3985,6 @@
       <c r="C102" t="s">
         <v>493</v>
       </c>
-      <c r="D102" t="s">
-        <v>485</v>
-      </c>
       <c r="E102" t="s">
         <v>162</v>
       </c>
@@ -4057,7 +3994,7 @@
         <v>163</v>
       </c>
       <c r="B103" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C103" t="s">
         <v>483</v>
@@ -4074,7 +4011,7 @@
         <v>164</v>
       </c>
       <c r="B104" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C104" t="s">
         <v>483</v>
@@ -4091,7 +4028,7 @@
         <v>166</v>
       </c>
       <c r="B105" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C105" t="s">
         <v>483</v>
@@ -4108,13 +4045,10 @@
         <v>167</v>
       </c>
       <c r="B106" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C106" t="s">
-        <v>522</v>
-      </c>
-      <c r="D106" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E106" t="s">
         <v>168</v>
@@ -4125,13 +4059,10 @@
         <v>169</v>
       </c>
       <c r="B107" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C107" t="s">
         <v>483</v>
-      </c>
-      <c r="D107" t="s">
-        <v>485</v>
       </c>
       <c r="E107" t="s">
         <v>168</v>
@@ -4142,7 +4073,7 @@
         <v>170</v>
       </c>
       <c r="B108" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C108" t="s">
         <v>483</v>
@@ -4159,7 +4090,7 @@
         <v>171</v>
       </c>
       <c r="B109" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C109" t="s">
         <v>483</v>
@@ -4176,7 +4107,7 @@
         <v>172</v>
       </c>
       <c r="B110" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C110" t="s">
         <v>483</v>
@@ -4193,7 +4124,7 @@
         <v>173</v>
       </c>
       <c r="B111" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C111" t="s">
         <v>483</v>
@@ -4210,7 +4141,7 @@
         <v>174</v>
       </c>
       <c r="B112" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C112" t="s">
         <v>483</v>
@@ -4227,7 +4158,7 @@
         <v>175</v>
       </c>
       <c r="B113" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C113" t="s">
         <v>483</v>
@@ -4244,7 +4175,7 @@
         <v>176</v>
       </c>
       <c r="B114" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C114" t="s">
         <v>483</v>
@@ -4261,7 +4192,7 @@
         <v>177</v>
       </c>
       <c r="B115" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C115" t="s">
         <v>483</v>
@@ -4278,7 +4209,7 @@
         <v>178</v>
       </c>
       <c r="B116" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C116" t="s">
         <v>483</v>
@@ -4397,7 +4328,7 @@
         <v>190</v>
       </c>
       <c r="B123" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C123" t="s">
         <v>483</v>
@@ -4414,7 +4345,7 @@
         <v>192</v>
       </c>
       <c r="B124" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C124" t="s">
         <v>483</v>
@@ -4431,7 +4362,7 @@
         <v>194</v>
       </c>
       <c r="B125" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C125" t="s">
         <v>483</v>
@@ -4465,7 +4396,7 @@
         <v>196</v>
       </c>
       <c r="B127" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C127" t="s">
         <v>483</v>
@@ -4482,10 +4413,10 @@
         <v>197</v>
       </c>
       <c r="B128" t="s">
-        <v>501</v>
+        <v>647</v>
       </c>
       <c r="C128" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="D128" t="s">
         <v>6</v>
@@ -4499,10 +4430,10 @@
         <v>198</v>
       </c>
       <c r="B129" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C129" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D129" t="s">
         <v>485</v>
@@ -4516,7 +4447,7 @@
         <v>200</v>
       </c>
       <c r="B130" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C130" t="s">
         <v>483</v>
@@ -4533,7 +4464,7 @@
         <v>201</v>
       </c>
       <c r="B131" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C131" t="s">
         <v>483</v>
@@ -4550,7 +4481,7 @@
         <v>202</v>
       </c>
       <c r="B132" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C132" t="s">
         <v>483</v>
@@ -4584,7 +4515,7 @@
         <v>204</v>
       </c>
       <c r="B134" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C134" t="s">
         <v>483</v>
@@ -4618,7 +4549,7 @@
         <v>207</v>
       </c>
       <c r="B136" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C136" t="s">
         <v>483</v>
@@ -4635,7 +4566,7 @@
         <v>208</v>
       </c>
       <c r="B137" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C137" t="s">
         <v>483</v>
@@ -4652,13 +4583,10 @@
         <v>209</v>
       </c>
       <c r="B138" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C138" t="s">
         <v>483</v>
-      </c>
-      <c r="D138" t="s">
-        <v>485</v>
       </c>
       <c r="E138" t="s">
         <v>41</v>
@@ -4669,7 +4597,7 @@
         <v>210</v>
       </c>
       <c r="B139" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C139" t="s">
         <v>483</v>
@@ -4686,7 +4614,7 @@
         <v>212</v>
       </c>
       <c r="B140" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C140" t="s">
         <v>483</v>
@@ -4822,13 +4750,10 @@
         <v>224</v>
       </c>
       <c r="B148" t="s">
-        <v>573</v>
+        <v>661</v>
       </c>
       <c r="C148" t="s">
-        <v>483</v>
-      </c>
-      <c r="D148" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E148" t="s">
         <v>168</v>
@@ -4907,7 +4832,7 @@
         <v>229</v>
       </c>
       <c r="B153" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C153" t="s">
         <v>483</v>
@@ -4924,7 +4849,7 @@
         <v>231</v>
       </c>
       <c r="B154" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C154" t="s">
         <v>483</v>
@@ -4941,7 +4866,7 @@
         <v>233</v>
       </c>
       <c r="B155" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C155" t="s">
         <v>483</v>
@@ -4958,7 +4883,7 @@
         <v>235</v>
       </c>
       <c r="B156" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C156" t="s">
         <v>483</v>
@@ -4975,13 +4900,10 @@
         <v>236</v>
       </c>
       <c r="B157" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C157" t="s">
-        <v>522</v>
-      </c>
-      <c r="D157" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E157" t="s">
         <v>66</v>
@@ -4992,13 +4914,10 @@
         <v>237</v>
       </c>
       <c r="B158" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C158" t="s">
-        <v>522</v>
-      </c>
-      <c r="D158" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E158" t="s">
         <v>19</v>
@@ -5009,13 +4928,10 @@
         <v>238</v>
       </c>
       <c r="B159" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C159" t="s">
-        <v>522</v>
-      </c>
-      <c r="D159" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E159" t="s">
         <v>19</v>
@@ -5026,13 +4942,10 @@
         <v>239</v>
       </c>
       <c r="B160" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C160" t="s">
-        <v>522</v>
-      </c>
-      <c r="D160" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E160" t="s">
         <v>240</v>
@@ -5043,7 +4956,7 @@
         <v>241</v>
       </c>
       <c r="B161" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C161" t="s">
         <v>483</v>
@@ -5060,7 +4973,7 @@
         <v>242</v>
       </c>
       <c r="B162" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C162" t="s">
         <v>483</v>
@@ -5077,7 +4990,7 @@
         <v>244</v>
       </c>
       <c r="B163" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C163" t="s">
         <v>483</v>
@@ -5094,7 +5007,7 @@
         <v>245</v>
       </c>
       <c r="B164" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C164" t="s">
         <v>483</v>
@@ -5179,7 +5092,7 @@
         <v>254</v>
       </c>
       <c r="B169" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C169" t="s">
         <v>489</v>
@@ -5196,7 +5109,7 @@
         <v>256</v>
       </c>
       <c r="B170" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C170" t="s">
         <v>489</v>
@@ -5213,7 +5126,7 @@
         <v>258</v>
       </c>
       <c r="B171" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C171" t="s">
         <v>483</v>
@@ -5230,7 +5143,7 @@
         <v>260</v>
       </c>
       <c r="B172" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C172" t="s">
         <v>483</v>
@@ -5247,13 +5160,10 @@
         <v>261</v>
       </c>
       <c r="B173" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C173" t="s">
-        <v>522</v>
-      </c>
-      <c r="D173" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E173" t="s">
         <v>69</v>
@@ -5264,13 +5174,10 @@
         <v>262</v>
       </c>
       <c r="B174" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C174" t="s">
-        <v>504</v>
-      </c>
-      <c r="D174" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="E174" t="s">
         <v>19</v>
@@ -5281,7 +5188,7 @@
         <v>263</v>
       </c>
       <c r="B175" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C175" t="s">
         <v>483</v>
@@ -5298,7 +5205,7 @@
         <v>264</v>
       </c>
       <c r="B176" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C176" t="s">
         <v>483</v>
@@ -5315,7 +5222,7 @@
         <v>265</v>
       </c>
       <c r="B177" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C177" t="s">
         <v>483</v>
@@ -5332,7 +5239,7 @@
         <v>266</v>
       </c>
       <c r="B178" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C178" t="s">
         <v>483</v>
@@ -5349,7 +5256,7 @@
         <v>268</v>
       </c>
       <c r="B179" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C179" t="s">
         <v>483</v>
@@ -5366,7 +5273,7 @@
         <v>269</v>
       </c>
       <c r="B180" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C180" t="s">
         <v>483</v>
@@ -5383,13 +5290,10 @@
         <v>270</v>
       </c>
       <c r="B181" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C181" t="s">
         <v>492</v>
-      </c>
-      <c r="D181" t="s">
-        <v>485</v>
       </c>
       <c r="E181" t="s">
         <v>219</v>
@@ -5400,13 +5304,10 @@
         <v>271</v>
       </c>
       <c r="B182" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C182" t="s">
         <v>492</v>
-      </c>
-      <c r="D182" t="s">
-        <v>485</v>
       </c>
       <c r="E182" t="s">
         <v>41</v>
@@ -5417,7 +5318,7 @@
         <v>272</v>
       </c>
       <c r="B183" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C183" t="s">
         <v>492</v>
@@ -5434,7 +5335,7 @@
         <v>273</v>
       </c>
       <c r="B184" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C184" t="s">
         <v>483</v>
@@ -5451,7 +5352,7 @@
         <v>274</v>
       </c>
       <c r="B185" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C185" t="s">
         <v>483</v>
@@ -5468,7 +5369,7 @@
         <v>275</v>
       </c>
       <c r="B186" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C186" t="s">
         <v>483</v>
@@ -5485,7 +5386,7 @@
         <v>276</v>
       </c>
       <c r="B187" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C187" t="s">
         <v>483</v>
@@ -5502,7 +5403,7 @@
         <v>278</v>
       </c>
       <c r="B188" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C188" t="s">
         <v>483</v>
@@ -5519,7 +5420,7 @@
         <v>280</v>
       </c>
       <c r="B189" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C189" t="s">
         <v>483</v>
@@ -5536,13 +5437,13 @@
         <v>281</v>
       </c>
       <c r="B190" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C190" t="s">
         <v>483</v>
       </c>
       <c r="D190" t="s">
-        <v>595</v>
+        <v>662</v>
       </c>
       <c r="E190" t="s">
         <v>282</v>
@@ -5553,7 +5454,7 @@
         <v>283</v>
       </c>
       <c r="B191" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C191" t="s">
         <v>483</v>
@@ -5570,10 +5471,10 @@
         <v>285</v>
       </c>
       <c r="B192" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C192" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D192" t="s">
         <v>6</v>
@@ -5587,7 +5488,7 @@
         <v>286</v>
       </c>
       <c r="B193" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C193" t="s">
         <v>483</v>
@@ -5604,13 +5505,10 @@
         <v>287</v>
       </c>
       <c r="B194" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C194" t="s">
         <v>489</v>
-      </c>
-      <c r="D194" t="s">
-        <v>485</v>
       </c>
       <c r="E194" t="s">
         <v>288</v>
@@ -5621,13 +5519,10 @@
         <v>289</v>
       </c>
       <c r="B195" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C195" t="s">
         <v>489</v>
-      </c>
-      <c r="D195" t="s">
-        <v>485</v>
       </c>
       <c r="E195" t="s">
         <v>290</v>
@@ -5638,13 +5533,10 @@
         <v>291</v>
       </c>
       <c r="B196" t="s">
-        <v>601</v>
+        <v>663</v>
       </c>
       <c r="C196" t="s">
-        <v>483</v>
-      </c>
-      <c r="D196" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E196" t="s">
         <v>64</v>
@@ -5655,13 +5547,10 @@
         <v>292</v>
       </c>
       <c r="B197" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C197" t="s">
         <v>483</v>
-      </c>
-      <c r="D197" t="s">
-        <v>485</v>
       </c>
       <c r="E197" t="s">
         <v>41</v>
@@ -5672,13 +5561,10 @@
         <v>293</v>
       </c>
       <c r="B198" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C198" t="s">
         <v>483</v>
-      </c>
-      <c r="D198" t="s">
-        <v>485</v>
       </c>
       <c r="E198" t="s">
         <v>75</v>
@@ -5689,13 +5575,10 @@
         <v>294</v>
       </c>
       <c r="B199" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C199" t="s">
         <v>483</v>
-      </c>
-      <c r="D199" t="s">
-        <v>485</v>
       </c>
       <c r="E199" t="s">
         <v>295</v>
@@ -5706,13 +5589,10 @@
         <v>296</v>
       </c>
       <c r="B200" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C200" t="s">
         <v>483</v>
-      </c>
-      <c r="D200" t="s">
-        <v>485</v>
       </c>
       <c r="E200" t="s">
         <v>19</v>
@@ -5723,13 +5603,10 @@
         <v>297</v>
       </c>
       <c r="B201" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C201" t="s">
         <v>483</v>
-      </c>
-      <c r="D201" t="s">
-        <v>485</v>
       </c>
       <c r="E201" t="s">
         <v>19</v>
@@ -5740,13 +5617,10 @@
         <v>298</v>
       </c>
       <c r="B202" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C202" t="s">
         <v>483</v>
-      </c>
-      <c r="D202" t="s">
-        <v>485</v>
       </c>
       <c r="E202" t="s">
         <v>299</v>
@@ -5791,7 +5665,7 @@
         <v>302</v>
       </c>
       <c r="B205" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C205" t="s">
         <v>492</v>
@@ -5825,7 +5699,7 @@
         <v>305</v>
       </c>
       <c r="B207" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C207" t="s">
         <v>483</v>
@@ -5842,7 +5716,7 @@
         <v>307</v>
       </c>
       <c r="B208" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C208" t="s">
         <v>483</v>
@@ -6046,7 +5920,7 @@
         <v>325</v>
       </c>
       <c r="B220" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C220" t="s">
         <v>483</v>
@@ -6063,7 +5937,7 @@
         <v>327</v>
       </c>
       <c r="B221" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C221" t="s">
         <v>483</v>
@@ -6080,7 +5954,7 @@
         <v>328</v>
       </c>
       <c r="B222" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C222" t="s">
         <v>483</v>
@@ -6097,7 +5971,7 @@
         <v>329</v>
       </c>
       <c r="B223" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C223" t="s">
         <v>483</v>
@@ -6114,7 +5988,7 @@
         <v>330</v>
       </c>
       <c r="B224" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C224" t="s">
         <v>483</v>
@@ -6131,10 +6005,10 @@
         <v>331</v>
       </c>
       <c r="B225" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C225" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D225" t="s">
         <v>6</v>
@@ -6165,7 +6039,7 @@
         <v>333</v>
       </c>
       <c r="B227" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C227" t="s">
         <v>483</v>
@@ -6182,7 +6056,7 @@
         <v>334</v>
       </c>
       <c r="B228" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C228" t="s">
         <v>483</v>
@@ -6199,7 +6073,7 @@
         <v>335</v>
       </c>
       <c r="B229" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C229" t="s">
         <v>483</v>
@@ -6216,13 +6090,10 @@
         <v>336</v>
       </c>
       <c r="B230" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="C230" t="s">
-        <v>487</v>
-      </c>
-      <c r="D230" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E230" t="s">
         <v>21</v>
@@ -6233,7 +6104,7 @@
         <v>337</v>
       </c>
       <c r="B231" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C231" t="s">
         <v>483</v>
@@ -6250,7 +6121,7 @@
         <v>338</v>
       </c>
       <c r="B232" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C232" t="s">
         <v>483</v>
@@ -6267,7 +6138,7 @@
         <v>339</v>
       </c>
       <c r="B233" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C233" t="s">
         <v>483</v>
@@ -6284,7 +6155,7 @@
         <v>340</v>
       </c>
       <c r="B234" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C234" t="s">
         <v>483</v>
@@ -6301,7 +6172,7 @@
         <v>341</v>
       </c>
       <c r="B235" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C235" t="s">
         <v>483</v>
@@ -6318,7 +6189,7 @@
         <v>343</v>
       </c>
       <c r="B236" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C236" t="s">
         <v>483</v>
@@ -6335,7 +6206,7 @@
         <v>344</v>
       </c>
       <c r="B237" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C237" t="s">
         <v>483</v>
@@ -6352,7 +6223,7 @@
         <v>345</v>
       </c>
       <c r="B238" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C238" t="s">
         <v>483</v>
@@ -6454,13 +6325,10 @@
         <v>353</v>
       </c>
       <c r="B244" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C244" t="s">
-        <v>504</v>
-      </c>
-      <c r="D244" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="E244" t="s">
         <v>118</v>
@@ -6471,7 +6339,7 @@
         <v>354</v>
       </c>
       <c r="B245" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C245" t="s">
         <v>483</v>
@@ -6485,13 +6353,10 @@
         <v>355</v>
       </c>
       <c r="B246" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C246" t="s">
         <v>483</v>
-      </c>
-      <c r="D246" t="s">
-        <v>485</v>
       </c>
       <c r="E246" t="s">
         <v>48</v>
@@ -6502,7 +6367,7 @@
         <v>356</v>
       </c>
       <c r="B247" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C247" t="s">
         <v>483</v>
@@ -6519,7 +6384,7 @@
         <v>358</v>
       </c>
       <c r="B248" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C248" t="s">
         <v>483</v>
@@ -6536,7 +6401,7 @@
         <v>360</v>
       </c>
       <c r="B249" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C249" t="s">
         <v>483</v>
@@ -6553,7 +6418,7 @@
         <v>361</v>
       </c>
       <c r="B250" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C250" t="s">
         <v>483</v>
@@ -6570,7 +6435,7 @@
         <v>362</v>
       </c>
       <c r="B251" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C251" t="s">
         <v>483</v>
@@ -6587,7 +6452,7 @@
         <v>364</v>
       </c>
       <c r="B252" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C252" t="s">
         <v>483</v>
@@ -6604,7 +6469,7 @@
         <v>365</v>
       </c>
       <c r="B253" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C253" t="s">
         <v>483</v>
@@ -6621,7 +6486,7 @@
         <v>366</v>
       </c>
       <c r="B254" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C254" t="s">
         <v>483</v>
@@ -6638,7 +6503,7 @@
         <v>368</v>
       </c>
       <c r="B255" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C255" t="s">
         <v>483</v>
@@ -6655,7 +6520,7 @@
         <v>369</v>
       </c>
       <c r="B256" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C256" t="s">
         <v>483</v>
@@ -6678,7 +6543,7 @@
         <v>493</v>
       </c>
       <c r="D257" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E257" t="s">
         <v>41</v>
@@ -6689,13 +6554,10 @@
         <v>371</v>
       </c>
       <c r="B258" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C258" t="s">
-        <v>522</v>
-      </c>
-      <c r="D258" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E258" t="s">
         <v>7</v>
@@ -6706,7 +6568,7 @@
         <v>372</v>
       </c>
       <c r="B259" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C259" t="s">
         <v>483</v>
@@ -6723,13 +6585,10 @@
         <v>374</v>
       </c>
       <c r="B260" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C260" t="s">
-        <v>522</v>
-      </c>
-      <c r="D260" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E260" t="s">
         <v>375</v>
@@ -6740,13 +6599,10 @@
         <v>376</v>
       </c>
       <c r="B261" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C261" t="s">
         <v>483</v>
-      </c>
-      <c r="D261" t="s">
-        <v>485</v>
       </c>
       <c r="E261" t="s">
         <v>41</v>
@@ -6757,7 +6613,7 @@
         <v>377</v>
       </c>
       <c r="B262" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C262" t="s">
         <v>483</v>
@@ -6774,13 +6630,10 @@
         <v>378</v>
       </c>
       <c r="B263" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C263" t="s">
         <v>492</v>
-      </c>
-      <c r="D263" t="s">
-        <v>485</v>
       </c>
       <c r="E263" t="s">
         <v>19</v>
@@ -6791,13 +6644,10 @@
         <v>379</v>
       </c>
       <c r="B264" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C264" t="s">
         <v>492</v>
-      </c>
-      <c r="D264" t="s">
-        <v>485</v>
       </c>
       <c r="E264" t="s">
         <v>380</v>
@@ -6808,13 +6658,10 @@
         <v>381</v>
       </c>
       <c r="B265" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C265" t="s">
         <v>483</v>
-      </c>
-      <c r="D265" t="s">
-        <v>485</v>
       </c>
       <c r="E265" t="s">
         <v>64</v>
@@ -6825,7 +6672,7 @@
         <v>382</v>
       </c>
       <c r="B266" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C266" t="s">
         <v>483</v>
@@ -6842,7 +6689,7 @@
         <v>384</v>
       </c>
       <c r="B267" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C267" t="s">
         <v>483</v>
@@ -6859,7 +6706,7 @@
         <v>385</v>
       </c>
       <c r="B268" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C268" t="s">
         <v>489</v>
@@ -6876,7 +6723,7 @@
         <v>387</v>
       </c>
       <c r="B269" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C269" t="s">
         <v>489</v>
@@ -6893,7 +6740,7 @@
         <v>389</v>
       </c>
       <c r="B270" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C270" t="s">
         <v>492</v>
@@ -6910,7 +6757,7 @@
         <v>391</v>
       </c>
       <c r="B271" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C271" t="s">
         <v>492</v>
@@ -6927,7 +6774,7 @@
         <v>393</v>
       </c>
       <c r="B272" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C272" t="s">
         <v>492</v>
@@ -7131,7 +6978,7 @@
         <v>408</v>
       </c>
       <c r="B284" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C284" t="s">
         <v>483</v>
@@ -7148,7 +6995,7 @@
         <v>409</v>
       </c>
       <c r="B285" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C285" t="s">
         <v>483</v>
@@ -7165,7 +7012,7 @@
         <v>411</v>
       </c>
       <c r="B286" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C286" t="s">
         <v>483</v>
@@ -7182,7 +7029,7 @@
         <v>412</v>
       </c>
       <c r="B287" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C287" t="s">
         <v>483</v>
@@ -7199,7 +7046,7 @@
         <v>413</v>
       </c>
       <c r="B288" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C288" t="s">
         <v>483</v>
@@ -7216,7 +7063,7 @@
         <v>415</v>
       </c>
       <c r="B289" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C289" t="s">
         <v>483</v>
@@ -7233,7 +7080,7 @@
         <v>416</v>
       </c>
       <c r="B290" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C290" t="s">
         <v>483</v>
@@ -7250,13 +7097,13 @@
         <v>417</v>
       </c>
       <c r="B291" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C291" t="s">
         <v>483</v>
       </c>
       <c r="D291" t="s">
-        <v>485</v>
+        <v>664</v>
       </c>
       <c r="E291" t="s">
         <v>19</v>
@@ -7267,7 +7114,7 @@
         <v>418</v>
       </c>
       <c r="B292" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C292" t="s">
         <v>483</v>
@@ -7284,7 +7131,7 @@
         <v>420</v>
       </c>
       <c r="B293" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C293" t="s">
         <v>483</v>
@@ -7301,7 +7148,7 @@
         <v>421</v>
       </c>
       <c r="B294" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C294" t="s">
         <v>483</v>
@@ -7318,7 +7165,7 @@
         <v>422</v>
       </c>
       <c r="B295" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C295" t="s">
         <v>483</v>
@@ -7335,7 +7182,7 @@
         <v>424</v>
       </c>
       <c r="B296" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C296" t="s">
         <v>483</v>
@@ -7352,7 +7199,7 @@
         <v>425</v>
       </c>
       <c r="B297" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C297" t="s">
         <v>483</v>
@@ -7369,7 +7216,7 @@
         <v>426</v>
       </c>
       <c r="B298" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C298" t="s">
         <v>483</v>
@@ -7386,7 +7233,7 @@
         <v>427</v>
       </c>
       <c r="B299" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C299" t="s">
         <v>483</v>
@@ -7403,7 +7250,7 @@
         <v>428</v>
       </c>
       <c r="B300" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C300" t="s">
         <v>483</v>
@@ -7420,7 +7267,7 @@
         <v>429</v>
       </c>
       <c r="B301" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C301" t="s">
         <v>483</v>
@@ -7437,7 +7284,7 @@
         <v>431</v>
       </c>
       <c r="B302" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C302" t="s">
         <v>483</v>
@@ -7454,7 +7301,7 @@
         <v>432</v>
       </c>
       <c r="B303" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C303" t="s">
         <v>483</v>
@@ -7471,13 +7318,10 @@
         <v>433</v>
       </c>
       <c r="B304" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C304" t="s">
-        <v>522</v>
-      </c>
-      <c r="D304" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E304" t="s">
         <v>64</v>
@@ -7488,7 +7332,7 @@
         <v>434</v>
       </c>
       <c r="B305" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C305" t="s">
         <v>483</v>
@@ -7505,7 +7349,7 @@
         <v>435</v>
       </c>
       <c r="B306" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C306" t="s">
         <v>483</v>
@@ -7522,7 +7366,7 @@
         <v>436</v>
       </c>
       <c r="B307" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C307" t="s">
         <v>483</v>
@@ -7539,7 +7383,7 @@
         <v>437</v>
       </c>
       <c r="B308" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C308" t="s">
         <v>483</v>
@@ -7556,7 +7400,7 @@
         <v>439</v>
       </c>
       <c r="B309" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C309" t="s">
         <v>483</v>
@@ -7573,7 +7417,7 @@
         <v>441</v>
       </c>
       <c r="B310" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C310" t="s">
         <v>483</v>
@@ -7590,7 +7434,7 @@
         <v>442</v>
       </c>
       <c r="B311" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C311" t="s">
         <v>483</v>
@@ -7607,7 +7451,7 @@
         <v>444</v>
       </c>
       <c r="B312" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C312" t="s">
         <v>483</v>
@@ -7658,13 +7502,10 @@
         <v>449</v>
       </c>
       <c r="B315" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C315" t="s">
         <v>483</v>
-      </c>
-      <c r="D315" t="s">
-        <v>485</v>
       </c>
       <c r="E315" t="s">
         <v>11</v>
@@ -7692,7 +7533,7 @@
         <v>451</v>
       </c>
       <c r="B317" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C317" t="s">
         <v>483</v>
@@ -7709,13 +7550,10 @@
         <v>453</v>
       </c>
       <c r="B318" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C318" t="s">
-        <v>522</v>
-      </c>
-      <c r="D318" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E318" t="s">
         <v>454</v>
@@ -7726,13 +7564,10 @@
         <v>455</v>
       </c>
       <c r="B319" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="C319" t="s">
-        <v>483</v>
-      </c>
-      <c r="D319" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E319" t="s">
         <v>456</v>
@@ -7743,7 +7578,7 @@
         <v>457</v>
       </c>
       <c r="B320" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C320" t="s">
         <v>483</v>
@@ -7760,13 +7595,10 @@
         <v>458</v>
       </c>
       <c r="B321" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C321" t="s">
         <v>483</v>
-      </c>
-      <c r="D321" t="s">
-        <v>485</v>
       </c>
       <c r="E321" t="s">
         <v>152</v>
@@ -7777,13 +7609,10 @@
         <v>459</v>
       </c>
       <c r="B322" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C322" t="s">
         <v>483</v>
-      </c>
-      <c r="D322" t="s">
-        <v>485</v>
       </c>
       <c r="E322" t="s">
         <v>168</v>
@@ -7794,7 +7623,7 @@
         <v>460</v>
       </c>
       <c r="B323" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C323" t="s">
         <v>483</v>
@@ -7811,13 +7640,10 @@
         <v>461</v>
       </c>
       <c r="B324" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C324" t="s">
-        <v>522</v>
-      </c>
-      <c r="D324" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E324" t="s">
         <v>462</v>
@@ -7828,13 +7654,10 @@
         <v>463</v>
       </c>
       <c r="B325" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C325" t="s">
-        <v>522</v>
-      </c>
-      <c r="D325" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E325" t="s">
         <v>26</v>
@@ -7845,13 +7668,10 @@
         <v>464</v>
       </c>
       <c r="B326" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C326" t="s">
-        <v>522</v>
-      </c>
-      <c r="D326" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E326" t="s">
         <v>19</v>
@@ -7862,7 +7682,7 @@
         <v>465</v>
       </c>
       <c r="B327" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C327" t="s">
         <v>483</v>
@@ -7879,7 +7699,7 @@
         <v>466</v>
       </c>
       <c r="B328" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C328" t="s">
         <v>483</v>
@@ -7896,7 +7716,7 @@
         <v>468</v>
       </c>
       <c r="B329" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C329" t="s">
         <v>483</v>
@@ -7913,7 +7733,7 @@
         <v>469</v>
       </c>
       <c r="B330" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C330" t="s">
         <v>483</v>
@@ -7930,7 +7750,7 @@
         <v>470</v>
       </c>
       <c r="B331" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C331" t="s">
         <v>483</v>
@@ -7947,7 +7767,7 @@
         <v>472</v>
       </c>
       <c r="B332" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C332" t="s">
         <v>483</v>
@@ -7964,7 +7784,7 @@
         <v>474</v>
       </c>
       <c r="B333" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C333" t="s">
         <v>483</v>
@@ -7981,13 +7801,10 @@
         <v>476</v>
       </c>
       <c r="B334" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C334" t="s">
-        <v>522</v>
-      </c>
-      <c r="D334" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E334" t="s">
         <v>19</v>
@@ -7998,13 +7815,10 @@
         <v>477</v>
       </c>
       <c r="B335" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C335" t="s">
-        <v>522</v>
-      </c>
-      <c r="D335" t="s">
-        <v>485</v>
+        <v>521</v>
       </c>
       <c r="E335" t="s">
         <v>21</v>
@@ -8015,7 +7829,7 @@
         <v>478</v>
       </c>
       <c r="B336" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C336" t="s">
         <v>483</v>
@@ -8032,7 +7846,7 @@
         <v>480</v>
       </c>
       <c r="B337" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C337" t="s">
         <v>483</v>
